--- a/UI仕様書フォーマット.xlsx
+++ b/UI仕様書フォーマット.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\中平　悠希\Desktop\GitHub\2025Summer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A83D1D-A254-413A-9E9F-24A4352F27A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963D250C-0BE6-4BAB-9DCD-BC58932E0418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="11" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
   </bookViews>
   <sheets>
     <sheet name="全体概要" sheetId="4" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Player仕様" sheetId="5" r:id="rId9"/>
     <sheet name="Enemy仕様" sheetId="6" r:id="rId10"/>
     <sheet name="リソースリスト" sheetId="2" r:id="rId11"/>
+    <sheet name="9月までにやりたいこと" sheetId="14" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="350">
   <si>
     <t>ロゴ</t>
     <phoneticPr fontId="1"/>
@@ -2629,6 +2630,403 @@
     <t>ちょっと待って</t>
     <rPh sb="4" eb="5">
       <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優先度</t>
+    <rPh sb="0" eb="3">
+      <t>ユウセンド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャンペーンモード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カテゴリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各ステージの敵のパターン</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵3種類</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーキャラクター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中攻撃(3連撃)</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>レンゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打ち上げ攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エネミー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打ち上げ耐久力</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>タイキュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サウンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果音</t>
+    <rPh sb="0" eb="3">
+      <t>コウカオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃コマンドを付け替えできる仕組み</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強化内容(コマンド各方向にそれぞれ2つは欲しい)</t>
+    <rPh sb="0" eb="2">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>カクホウコウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームの流れ</t>
+    <rPh sb="4" eb="5">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡後シーン遷移</t>
+    <rPh sb="0" eb="3">
+      <t>シボウゴ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やりたいことまとめ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ4つ(モデル)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アリーナモード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>演出</t>
+    <rPh sb="0" eb="2">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵のパターン</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>先に進むほど同じ敵でも強くなるシステム</t>
+    <rPh sb="0" eb="1">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うまくプレイするほど強化を豪華にする</t>
+    <rPh sb="10" eb="12">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゴウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うまくプレイするほどスコアが上がる</t>
+    <rPh sb="14" eb="15">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘全般</t>
+    <rPh sb="0" eb="2">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンパン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタイリッシュランクによるBGMの盛り上がり</t>
+    <rPh sb="17" eb="18">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダウン状態、空中ダウン状態</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スコアのセーブデータへの記録</t>
+    <rPh sb="12" eb="14">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強化状態のセーブデータへの記録</t>
+    <rPh sb="0" eb="4">
+      <t>キョウカジョウタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→攻撃6種類</t>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタイリッシュランクの調整(うまいプレイを反映)</t>
+    <rPh sb="11" eb="13">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スコアをセーブデータから読み出す</t>
+    <rPh sb="12" eb="13">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>並べて表示する</t>
+    <rPh sb="0" eb="1">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動画</t>
+    <rPh sb="0" eb="2">
+      <t>ドウガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃モーションのプレビュー動画</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ドウガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(強化時、スキルリスト表示時に表示)</t>
+    <rPh sb="1" eb="3">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ヒョウジジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルのデモプレイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定された操作をさせる仕組み</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ(ほかのゲームモードを流用してもよい)</t>
+    <rPh sb="15" eb="17">
+      <t>リュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エリートエネミーのモーションを改善したい</t>
+    <rPh sb="15" eb="17">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→回転時に足踏みしてほしい、他</t>
+    <rPh sb="1" eb="4">
+      <t>カイテンジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>アシブ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ホカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>音量調節</t>
+    <rPh sb="0" eb="4">
+      <t>オンリョウチョウセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ反転</t>
+    <rPh sb="3" eb="5">
+      <t>ハンテン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3055,7 +3453,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3201,6 +3599,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7476,6 +7877,279 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B43C49D-EE0E-4BF4-846E-C94855B25D7A}">
+  <dimension ref="A1:Z46"/>
+  <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="A1" s="49" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" s="49" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="16"/>
+      <c r="X3" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="Y3" s="16"/>
+      <c r="Z3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>305</v>
+      </c>
+      <c r="I4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="I5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="I6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="I7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="I8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="I9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="I10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="I11" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="I12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="I13" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>323</v>
+      </c>
+      <c r="I16" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I17" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I18" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I19" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I20" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I22" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
+        <v>330</v>
+      </c>
+      <c r="I23" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I24" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B25" t="s">
+        <v>309</v>
+      </c>
+      <c r="I25" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I26" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I27" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I28" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
+        <v>312</v>
+      </c>
+      <c r="I30" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I31" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I32" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I33" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B34" t="s">
+        <v>314</v>
+      </c>
+      <c r="I34" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I35" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I37" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B38" t="s">
+        <v>340</v>
+      </c>
+      <c r="I38" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I39" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I40" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B41" t="s">
+        <v>124</v>
+      </c>
+      <c r="I41" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I42" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I43" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B44" t="s">
+        <v>53</v>
+      </c>
+      <c r="I44" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I45" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I46" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{284E1E08-A810-409F-AFDE-590F7075CD00}">
   <dimension ref="A2:Q53"/>
@@ -10255,6 +10929,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="215e7263a294d62634617b65be5e81fd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6aa5db53fbf3e176f355664c77c2c9ef" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -10455,15 +11138,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5133F06B-0556-4887-9A4E-22EA032BC896}">
   <ds:schemaRefs>
@@ -10476,6 +11150,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49EC609C-331C-4105-80CF-9D6A995C6BFB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10492,12 +11174,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF99FEAD-80A2-47F3-ACCA-BE8E1C14FBEC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/UI仕様書フォーマット.xlsx
+++ b/UI仕様書フォーマット.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963D250C-0BE6-4BAB-9DCD-BC58932E0418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF1766C-3748-4141-B2F2-22BE9E476C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="3" activeTab="11" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="4" activeTab="12" xr2:uid="{DF94D868-592B-4338-B7CA-B1CACE85BD54}"/>
   </bookViews>
   <sheets>
     <sheet name="全体概要" sheetId="4" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="Enemy仕様" sheetId="6" r:id="rId10"/>
     <sheet name="リソースリスト" sheetId="2" r:id="rId11"/>
     <sheet name="9月までにやりたいこと" sheetId="14" r:id="rId12"/>
+    <sheet name="メモ" sheetId="15" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="366">
   <si>
     <t>ロゴ</t>
     <phoneticPr fontId="1"/>
@@ -3027,6 +3028,88 @@
     <t>カメラ反転</t>
     <rPh sb="3" eb="5">
       <t>ハンテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技</t>
+    <rPh sb="0" eb="1">
+      <t>ワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃技</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回避技</t>
+    <rPh sb="0" eb="3">
+      <t>カイヒワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Actorcontroller</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Physics</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Collidable</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Collider</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rigid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIController</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>位置データ</t>
+    <rPh sb="0" eb="2">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIPositionStore</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SceneUIPos</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>編集</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8150,6 +8233,82 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A3D13C-AD92-4326-A839-9A5F8A35AE3A}">
+  <dimension ref="G3:AM15"/>
+  <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="3" spans="7:39" x14ac:dyDescent="0.4">
+      <c r="O3" t="s">
+        <v>350</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="5" spans="7:39" x14ac:dyDescent="0.4">
+      <c r="L5" t="s">
+        <v>351</v>
+      </c>
+      <c r="O5" t="s">
+        <v>352</v>
+      </c>
+      <c r="R5" t="s">
+        <v>353</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="7" spans="7:39" x14ac:dyDescent="0.4">
+      <c r="AK7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="7:39" x14ac:dyDescent="0.4">
+      <c r="AI9" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12" spans="7:39" x14ac:dyDescent="0.4">
+      <c r="R12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="7:39" x14ac:dyDescent="0.4">
+      <c r="G13" t="s">
+        <v>359</v>
+      </c>
+      <c r="L13" t="s">
+        <v>363</v>
+      </c>
+      <c r="R13" t="s">
+        <v>361</v>
+      </c>
+      <c r="T13" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="15" spans="7:39" x14ac:dyDescent="0.4">
+      <c r="H15" t="s">
+        <v>360</v>
+      </c>
+      <c r="J15" t="s">
+        <v>361</v>
+      </c>
+      <c r="L15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{284E1E08-A810-409F-AFDE-590F7075CD00}">
   <dimension ref="A2:Q53"/>
